--- a/artfynd/A 5755-2025 artfynd.xlsx
+++ b/artfynd/A 5755-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100227266</v>
+        <v>100227167</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650448.9569983626</v>
+        <v>650449</v>
       </c>
       <c r="R2" t="n">
-        <v>6644657.96624452</v>
+        <v>6644658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +751,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,29 +776,14 @@
           <t>Beteshage med stora ekar och hassel</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Död hasselstam i hasselbukett</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Corylus avellana # Död hasselstam i hasselbukett</t>
+          <t>Stone/rock on land # Flyttblock</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -841,12 +808,7 @@
         <v>100227081</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650437.5824690601</v>
+        <v>650438</v>
       </c>
       <c r="R3" t="n">
-        <v>6644702.692025669</v>
+        <v>6644703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,19 +884,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,15 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100227167</v>
+        <v>100227266</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,31 +964,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1049,10 +999,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650448.9569983626</v>
+        <v>650449</v>
       </c>
       <c r="R4" t="n">
-        <v>6644657.96624452</v>
+        <v>6644658</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1082,19 +1032,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1117,14 +1057,29 @@
           <t>Beteshage med stora ekar och hassel</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Död hasselstam i hasselbukett</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stone/rock on land # Flyttblock</t>
+          <t>Standing dead tree/snags # Corylus avellana # Död hasselstam i hasselbukett</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
